--- a/Benchmarks/Water Chemistry/Conductivity/Var selection decisions 1-8-26.xlsx
+++ b/Benchmarks/Water Chemistry/Conductivity/Var selection decisions 1-8-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateoforegon-my.sharepoint.com/personal/sabine_berzins_deq_oregon_gov/Documents/Documents/BioMonORDEQ/Benchmarks/Water Chemistry/Conductivity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{6B8D232A-EEA6-4563-A1A6-87C6EEBA49F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98521123-257F-441E-9E67-17EC12A33FE4}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{6B8D232A-EEA6-4563-A1A6-87C6EEBA49F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9FAE374-0630-4F15-95EF-D1C8C7DC68F3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="1040" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Benchmarks/Water Chemistry/Conductivity/Var selection decisions 1-8-26.xlsx
+++ b/Benchmarks/Water Chemistry/Conductivity/Var selection decisions 1-8-26.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="18" documentId="8_{6B8D232A-EEA6-4563-A1A6-87C6EEBA49F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9FAE374-0630-4F15-95EF-D1C8C7DC68F3}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="1040" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-9690" yWindow="1150" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Benchmarks/Water Chemistry/Conductivity/Var selection decisions 1-8-26.xlsx
+++ b/Benchmarks/Water Chemistry/Conductivity/Var selection decisions 1-8-26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateoforegon-my.sharepoint.com/personal/sabine_berzins_deq_oregon_gov/Documents/Documents/BioMonORDEQ/Benchmarks/Water Chemistry/Conductivity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{6B8D232A-EEA6-4563-A1A6-87C6EEBA49F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9FAE374-0630-4F15-95EF-D1C8C7DC68F3}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{6B8D232A-EEA6-4563-A1A6-87C6EEBA49F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D29E22D7-EE0B-4CF3-BAC3-6462874E21AA}"/>
   <bookViews>
-    <workbookView xWindow="-9690" yWindow="1150" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="1040" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1065,6 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D140"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1088,7 +1089,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -1102,7 +1103,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -1113,7 +1114,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -1124,7 +1125,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
@@ -1138,7 +1139,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -1149,7 +1150,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -1157,7 +1158,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -1168,7 +1169,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -1190,7 +1191,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -1204,7 +1205,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
@@ -1215,7 +1216,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
@@ -1229,7 +1230,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1245,7 +1246,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>15</v>
       </c>
@@ -1259,7 +1260,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>16</v>
       </c>
@@ -1271,7 +1272,7 @@
       </c>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>17</v>
       </c>
@@ -1283,7 +1284,7 @@
       </c>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
@@ -1297,7 +1298,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -1305,7 +1306,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -1330,7 +1331,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>22</v>
       </c>
@@ -1341,7 +1342,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>23</v>
       </c>
@@ -1368,7 +1369,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>26</v>
       </c>
@@ -1390,17 +1391,17 @@
         <v>210</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>30</v>
       </c>
@@ -1411,7 +1412,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>31</v>
       </c>
@@ -1419,7 +1420,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>32</v>
       </c>
@@ -1430,7 +1431,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>33</v>
       </c>
@@ -1438,12 +1439,12 @@
         <v>164</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>35</v>
       </c>
@@ -1454,7 +1455,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>36</v>
       </c>
@@ -1468,7 +1469,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>37</v>
       </c>
@@ -1479,7 +1480,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>38</v>
       </c>
@@ -1490,7 +1491,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>39</v>
       </c>
@@ -1501,7 +1502,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>40</v>
       </c>
@@ -1512,7 +1513,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>41</v>
       </c>
@@ -1523,7 +1524,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>42</v>
       </c>
@@ -1531,7 +1532,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>43</v>
       </c>
@@ -1542,12 +1543,12 @@
         <v>195</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>45</v>
       </c>
@@ -1558,7 +1559,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>46</v>
       </c>
@@ -1566,13 +1567,13 @@
         <v>155</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>47</v>
       </c>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>48</v>
       </c>
@@ -1584,7 +1585,7 @@
       </c>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>49</v>
       </c>
@@ -1598,7 +1599,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>50</v>
       </c>
@@ -1606,7 +1607,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>51</v>
       </c>
@@ -1618,7 +1619,7 @@
       </c>
       <c r="D52" s="6"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>52</v>
       </c>
@@ -1630,22 +1631,22 @@
       </c>
       <c r="D53" s="6"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>56</v>
       </c>
@@ -1656,7 +1657,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>57</v>
       </c>
@@ -1667,7 +1668,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>58</v>
       </c>
@@ -1678,12 +1679,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>60</v>
       </c>
@@ -1691,32 +1692,32 @@
         <v>156</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>66</v>
       </c>
@@ -1730,7 +1731,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>67</v>
       </c>
@@ -1738,7 +1739,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>68</v>
       </c>
@@ -1746,13 +1747,13 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>69</v>
       </c>
       <c r="D70" s="6"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>70</v>
       </c>
@@ -1764,13 +1765,13 @@
       </c>
       <c r="D71" s="6"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D72" s="6"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>72</v>
       </c>
@@ -1782,12 +1783,12 @@
       </c>
       <c r="D73" s="6"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>74</v>
       </c>
@@ -1798,12 +1799,12 @@
         <v>197</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>76</v>
       </c>
@@ -1814,7 +1815,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>77</v>
       </c>
@@ -1825,12 +1826,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>79</v>
       </c>
@@ -1841,7 +1842,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>80</v>
       </c>
@@ -1852,7 +1853,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>81</v>
       </c>
@@ -1863,12 +1864,12 @@
         <v>201</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>83</v>
       </c>
@@ -1879,7 +1880,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>84</v>
       </c>
@@ -1890,7 +1891,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>85</v>
       </c>
@@ -1901,12 +1902,12 @@
         <v>189</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>87</v>
       </c>
@@ -1917,7 +1918,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>88</v>
       </c>
@@ -1928,12 +1929,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>90</v>
       </c>
@@ -1941,7 +1942,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>91</v>
       </c>
@@ -1949,7 +1950,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>92</v>
       </c>
@@ -1960,7 +1961,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>93</v>
       </c>
@@ -1971,12 +1972,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>95</v>
       </c>
@@ -1987,7 +1988,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>96</v>
       </c>
@@ -1998,17 +1999,17 @@
         <v>203</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>99</v>
       </c>
@@ -2016,7 +2017,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>100</v>
       </c>
@@ -2027,7 +2028,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>101</v>
       </c>
@@ -2035,7 +2036,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>102</v>
       </c>
@@ -2049,7 +2050,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>103</v>
       </c>
@@ -2060,7 +2061,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>104</v>
       </c>
@@ -2074,7 +2075,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>105</v>
       </c>
@@ -2086,7 +2087,7 @@
       </c>
       <c r="D106" s="6"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>106</v>
       </c>
@@ -2098,12 +2099,12 @@
       </c>
       <c r="D107" s="6"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>108</v>
       </c>
@@ -2111,24 +2112,24 @@
         <v>152</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>109</v>
       </c>
       <c r="D110" s="7"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>110</v>
       </c>
       <c r="D111" s="7"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>112</v>
       </c>
@@ -2142,7 +2143,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>113</v>
       </c>
@@ -2161,7 +2162,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>115</v>
       </c>
@@ -2169,7 +2170,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>116</v>
       </c>
@@ -2180,7 +2181,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>117</v>
       </c>
@@ -2191,7 +2192,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>118</v>
       </c>
@@ -2199,17 +2200,17 @@
         <v>150</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>121</v>
       </c>
@@ -2225,7 +2226,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>123</v>
       </c>
@@ -2236,7 +2237,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>124</v>
       </c>
@@ -2250,7 +2251,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>125</v>
       </c>
@@ -2262,7 +2263,7 @@
       </c>
       <c r="D126" s="6"/>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>126</v>
       </c>
@@ -2271,7 +2272,7 @@
       </c>
       <c r="D127" s="6"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>127</v>
       </c>
@@ -2280,7 +2281,7 @@
       </c>
       <c r="D128" s="6"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
         <v>128</v>
       </c>
@@ -2289,7 +2290,7 @@
       </c>
       <c r="D129" s="6"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>129</v>
       </c>
@@ -2298,7 +2299,7 @@
       </c>
       <c r="D130" s="6"/>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>130</v>
       </c>
@@ -2307,12 +2308,12 @@
       </c>
       <c r="D131" s="6"/>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>132</v>
       </c>
@@ -2323,7 +2324,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>133</v>
       </c>
@@ -2337,12 +2338,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>135</v>
       </c>
@@ -2356,12 +2357,12 @@
         <v>169</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>137</v>
       </c>
@@ -2375,7 +2376,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>138</v>
       </c>
@@ -2387,7 +2388,7 @@
       </c>
       <c r="D139" s="6"/>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>139</v>
       </c>
@@ -2400,7 +2401,13 @@
       <c r="D140" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D140" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:D140" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="not using composite index"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="8">
     <mergeCell ref="D16:D18"/>
     <mergeCell ref="D69:D73"/>
